--- a/codelists/all/HYP_CODES_MASTER.xlsx
+++ b/codelists/all/HYP_CODES_MASTER.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F352"/>
+  <dimension ref="A1:F363"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>127991000119101</t>
+          <t>118781000119108</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hypertension concurrent and due to end stage renal disease on dialysis due to type 2 diabetes mellitus (disorder)</t>
+          <t>Pre-existing hypertensive chronic kidney disease in mother complicating pregnancy (disorder)</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>128001000119105</t>
+          <t>127991000119101</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hypertension concurrent and due to end stage renal disease on dialysis due to type 1 diabetes mellitus (disorder)</t>
+          <t>Hypertension concurrent and due to end stage renal disease on dialysis due to type 2 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>132721000119104</t>
+          <t>128001000119105</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hypertensive emergency (disorder)</t>
+          <t>Hypertension concurrent and due to end stage renal disease on dialysis due to type 1 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>140101000119109</t>
+          <t>132721000119104</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 5 due to type 2 diabetes mellitus (disorder)</t>
+          <t>Hypertensive emergency (disorder)</t>
         </is>
       </c>
     </row>
@@ -2809,12 +2809,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>140111000119107</t>
+          <t>140101000119109</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 4 due to type 2 diabetes mellitus (disorder)</t>
+          <t>Hypertension in chronic kidney disease stage 5 due to type 2 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>140121000119100</t>
+          <t>140111000119107</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 3 due to type 2 diabetes mellitus (disorder)</t>
+          <t>Hypertension in chronic kidney disease stage 4 due to type 2 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>140131000119102</t>
+          <t>140121000119100</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 2 due to type 2 diabetes mellitus (disorder)</t>
+          <t>Hypertension in chronic kidney disease stage 3 due to type 2 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>367821000119106</t>
+          <t>140131000119102</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hypertension due to compression of renal parenchyma (disorder)</t>
+          <t>Hypertension in chronic kidney disease stage 2 due to type 2 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>843821000000102</t>
+          <t>367821000119106</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stage 1 hypertension (National Institute for Health and Clinical Excellence 2011) (disorder)</t>
+          <t>Hypertension due to compression of renal parenchyma (disorder)</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>843841000000109</t>
+          <t>843821000000102</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Severe hypertension (National Institute for Health and Clinical Excellence 2011) (disorder)</t>
+          <t>Stage 1 hypertension (National Institute for Health and Clinical Excellence 2011) (disorder)</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>845891000000103</t>
+          <t>843841000000109</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hypertension resistant to drug therapy (disorder)</t>
+          <t>Severe hypertension (National Institute for Health and Clinical Excellence 2011) (disorder)</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>846371000000103</t>
+          <t>845891000000103</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stage 2 hypertension (National Institute for Health and Clinical Excellence 2011) (disorder)</t>
+          <t>Hypertension resistant to drug therapy (disorder)</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3065,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>863191000000102</t>
+          <t>846371000000103</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nocturnal hypertension (disorder)</t>
+          <t>Stage 2 hypertension (National Institute for Health and Clinical Excellence 2011) (disorder)</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>908631000000108</t>
+          <t>863191000000102</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stage 1 hypertension (National Institute for Health and Clinical Excellence 2011) without evidence of end organ damage (disorder)</t>
+          <t>Nocturnal hypertension (disorder)</t>
         </is>
       </c>
     </row>
@@ -3129,12 +3129,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>908651000000101</t>
+          <t>908631000000108</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stage 1 hypertension (National Institute for Health and Clinical Excellence 2011) with evidence of end organ damage (disorder)</t>
+          <t>Stage 1 hypertension (National Institute for Health and Clinical Excellence 2011) without evidence of end organ damage (disorder)</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1078301000112109</t>
+          <t>908651000000101</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Multiple drug intolerant hypertension (disorder)</t>
+          <t>Stage 1 hypertension (National Institute for Health and Clinical Excellence 2011) with evidence of end organ damage (disorder)</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>10752641000119102</t>
+          <t>1078301000112109</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eclampsia with pre-existing hypertension in childbirth (disorder)</t>
+          <t>Multiple drug intolerant hypertension (disorder)</t>
         </is>
       </c>
     </row>
@@ -3225,12 +3225,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>10757401000119104</t>
+          <t>10752641000119102</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pre-existing hypertensive heart and chronic kidney disease in mother complicating childbirth (disorder)</t>
+          <t>Eclampsia with pre-existing hypertension in childbirth (disorder)</t>
         </is>
       </c>
     </row>
@@ -3257,12 +3257,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>10757441000119102</t>
+          <t>10757401000119104</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pre-existing hypertensive heart disease in mother complicating childbirth (disorder)</t>
+          <t>Pre-existing hypertensive heart and chronic kidney disease in mother complicating childbirth (disorder)</t>
         </is>
       </c>
     </row>
@@ -3289,12 +3289,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>10757481000119107</t>
+          <t>10757441000119102</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pre-existing hypertensive heart and chronic kidney disease in mother complicating pregnancy (disorder)</t>
+          <t>Pre-existing hypertensive heart disease in mother complicating childbirth (disorder)</t>
         </is>
       </c>
     </row>
@@ -3321,12 +3321,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>10759031000119106</t>
+          <t>10757481000119107</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pre-existing hypertensive heart disease in mother complicating pregnancy (disorder)</t>
+          <t>Pre-existing hypertensive heart and chronic kidney disease in mother complicating pregnancy (disorder)</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>16229371000119106</t>
+          <t>10759031000119106</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Labile systemic arterial hypertension (disorder)</t>
+          <t>Pre-existing hypertensive heart disease in mother complicating pregnancy (disorder)</t>
         </is>
       </c>
     </row>
@@ -3385,12 +3385,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>23130000</t>
+          <t>16229371000119106</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Paroxysmal hypertension (disorder)</t>
+          <t>Labile systemic arterial hypertension (disorder)</t>
         </is>
       </c>
     </row>
@@ -3417,12 +3417,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>429198000</t>
+          <t>59997006</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Exertional hypertension (disorder)</t>
+          <t>Endocrine hypertension (disorder)</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>697929007</t>
+          <t>198944004</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Intermittent hypertension (disorder)</t>
+          <t>Benign essential hypertension complicating pregnancy, childbirth and the puerperium - delivered (disorder)</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>698640000</t>
+          <t>198945003</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hypertension in the puerperium with pulmonary edema (disorder)</t>
+          <t>Benign essential hypertension complicating pregnancy, childbirth and the puerperium - delivered with postnatal complication (disorder)</t>
         </is>
       </c>
     </row>
@@ -3513,12 +3513,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1332436006</t>
+          <t>198946002</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 3B due to type 1 diabetes mellitus (disorder)</t>
+          <t>Benign essential hypertension complicating pregnancy, childbirth and the puerperium - not delivered (disorder)</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1332441003</t>
+          <t>198947006</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 3A due to type 1 diabetes mellitus (disorder)</t>
+          <t>Benign essential hypertension complicating pregnancy, childbirth and the puerperium with postnatal complication (disorder)</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1332442005</t>
+          <t>198999008</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 3 due to type 1 diabetes mellitus (disorder)</t>
+          <t>Pre-eclampsia or eclampsia with pre-existing hypertension - delivered (disorder)</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1332464001</t>
+          <t>199000005</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 2 due to type 1 diabetes mellitus (disorder)</t>
+          <t>Pre-eclampsia or eclampsia with pre-existing hypertension - delivered with postnatal complication (disorder)</t>
         </is>
       </c>
     </row>
@@ -3641,12 +3641,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1332465000</t>
+          <t>199002002</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 3B due to type 2 diabetes mellitus (disorder)</t>
+          <t>Pre-eclampsia or eclampsia with pre-existing hypertension - not delivered (disorder)</t>
         </is>
       </c>
     </row>
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1332466004</t>
+          <t>199003007</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 3A due to type 2 diabetes mellitus (disorder)</t>
+          <t>Pre-eclampsia or eclampsia with pre-existing hypertension with postnatal complication (disorder)</t>
         </is>
       </c>
     </row>
@@ -3705,12 +3705,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1332467008</t>
+          <t>471521000000108</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 5 due to type 1 diabetes mellitus (disorder)</t>
+          <t>[X]Hypertensive diseases (disorder)</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1332468003</t>
+          <t>23130000</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Hypertension in chronic kidney disease stage 4 due to type 1 diabetes mellitus (disorder)</t>
+          <t>Paroxysmal hypertension (disorder)</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3769,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1356877007</t>
+          <t>429198000</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stable hypertension (disorder)</t>
+          <t>Exertional hypertension (disorder)</t>
         </is>
       </c>
     </row>
@@ -3786,27 +3786,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HYPRES_COD</t>
+          <t>HYP_COD</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>999006531000230101</t>
+          <t>999006611000230105</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Hypertension resolved codes</t>
+          <t>Hypertension diagnosis codes</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>162659009</t>
+          <t>697929007</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hypertension resolved (finding)</t>
+          <t>Intermittent hypertension (disorder)</t>
         </is>
       </c>
     </row>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HYPRES_COD</t>
+          <t>HYP_COD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>999006531000230101</t>
+          <t>999006611000230105</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Hypertension resolved codes</t>
+          <t>Hypertension diagnosis codes</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>167031000000101</t>
+          <t>698640000</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hypertension resolved</t>
+          <t>Hypertension in the puerperium with pulmonary edema (disorder)</t>
         </is>
       </c>
     </row>
@@ -3850,379 +3850,379 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>HYPRES_COD</t>
+          <t>HYP_COD</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>999006531000230101</t>
+          <t>999006611000230105</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Hypertension resolved codes</t>
+          <t>Hypertension diagnosis codes</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>171791000000104</t>
+          <t>1332436006</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hypertension resolved</t>
+          <t>Hypertension in chronic kidney disease stage 3B due to type 1 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP_REG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ABPMDEC_COD</t>
+          <t>HYP_COD</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>999028531000230107</t>
+          <t>999006611000230105</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Codes indicating patient has chosen not to undertake ambulatory blood pressure monitoring (ABPM)</t>
+          <t>Hypertension diagnosis codes</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>861231000000105</t>
+          <t>1332441003</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ambulatory blood pressure recording declined (situation)</t>
+          <t>Hypertension in chronic kidney disease stage 3A due to type 1 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP_REG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ABPMDEC_COD</t>
+          <t>HYP_COD</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>999028531000230107</t>
+          <t>999006611000230105</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Codes indicating patient has chosen not to undertake ambulatory blood pressure monitoring (ABPM)</t>
+          <t>Hypertension diagnosis codes</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>861241000000101</t>
+          <t>1332442005</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ambulatory blood pressure recording declined</t>
+          <t>Hypertension in chronic kidney disease stage 3 due to type 1 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP_REG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BPDEC_COD</t>
+          <t>HYP_COD</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>999012611000230106</t>
+          <t>999006611000230105</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
+          <t>Hypertension diagnosis codes</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>413123006</t>
+          <t>1332464001</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blood pressure procedure declined (situation)</t>
+          <t>Hypertension in chronic kidney disease stage 2 due to type 1 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP_REG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BPDEC_COD</t>
+          <t>HYP_COD</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>999012611000230106</t>
+          <t>999006611000230105</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
+          <t>Hypertension diagnosis codes</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>117221000000107</t>
+          <t>1332465000</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blood pressure procedure refused</t>
+          <t>Hypertension in chronic kidney disease stage 3B due to type 2 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP_REG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BPDEC_COD</t>
+          <t>HYP_COD</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>999012611000230106</t>
+          <t>999006611000230105</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
+          <t>Hypertension diagnosis codes</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>121961000000108</t>
+          <t>1332466004</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blood pressure procedure refused</t>
+          <t>Hypertension in chronic kidney disease stage 3A due to type 2 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP_REG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYP_COD</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999006611000230105</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Hypertension diagnosis codes</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>6797001</t>
+          <t>1332467008</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mean blood pressure (observable entity)</t>
+          <t>Hypertension in chronic kidney disease stage 5 due to type 1 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP_REG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYP_COD</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999006611000230105</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Hypertension diagnosis codes</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>72313002</t>
+          <t>1332468003</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Systolic arterial pressure (observable entity)</t>
+          <t>Hypertension in chronic kidney disease stage 4 due to type 1 diabetes mellitus (disorder)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP_REG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYP_COD</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999006611000230105</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Hypertension diagnosis codes</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>75367002</t>
+          <t>1356877007</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blood pressure (observable entity)</t>
+          <t>Stable hypertension (disorder)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP_REG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYPRES_COD</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999006531000230101</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Hypertension resolved codes</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>163035008</t>
+          <t>162659009</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sitting blood pressure (observable entity)</t>
+          <t>Hypertension resolved (finding)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP_REG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYPRES_COD</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999006531000230101</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Hypertension resolved codes</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>174255007</t>
+          <t>167031000000101</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Non-invasive diastolic arterial pressure (observable entity)</t>
+          <t>Hypertension resolved</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP_REG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYPRES_COD</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999006531000230101</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Hypertension resolved codes</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>251070002</t>
+          <t>171791000000104</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Non-invasive systolic arterial pressure (observable entity)</t>
+          <t>Hypertension resolved</t>
         </is>
       </c>
     </row>
@@ -4234,27 +4234,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>ABPMDEC_COD</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999028531000230107</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Codes indicating patient has chosen not to undertake ambulatory blood pressure monitoring (ABPM)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>251076008</t>
+          <t>861231000000105</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Non-invasive arterial pressure (observable entity)</t>
+          <t>Ambulatory blood pressure recording declined (situation)</t>
         </is>
       </c>
     </row>
@@ -4266,27 +4266,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>ABPMDEC_COD</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999028531000230107</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Codes indicating patient has chosen not to undertake ambulatory blood pressure monitoring (ABPM)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>271649006</t>
+          <t>861241000000101</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Systolic blood pressure (observable entity)</t>
+          <t>Ambulatory blood pressure recording declined</t>
         </is>
       </c>
     </row>
@@ -4298,27 +4298,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>BPDEC_COD</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012611000230106</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>271650006</t>
+          <t>413123006</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure procedure declined (situation)</t>
         </is>
       </c>
     </row>
@@ -4330,27 +4330,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>BPDEC_COD</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012611000230106</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>314440001</t>
+          <t>117221000000107</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Average systolic blood pressure (observable entity)</t>
+          <t>Blood pressure procedure refused</t>
         </is>
       </c>
     </row>
@@ -4362,27 +4362,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>BPDEC_COD</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012611000230106</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>314453003</t>
+          <t>121961000000108</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Average diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure procedure refused</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>364090009</t>
+          <t>6797001</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Systemic arterial pressure (observable entity)</t>
+          <t>Mean blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>386534000</t>
+          <t>72313002</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Arterial blood pressure (observable entity)</t>
+          <t>Systolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4473,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>386536003</t>
+          <t>75367002</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Systemic blood pressure (observable entity)</t>
+          <t>Blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4505,12 +4505,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>407554009</t>
+          <t>163035008</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sitting systolic blood pressure (observable entity)</t>
+          <t>Sitting blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4537,12 +4537,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>407555005</t>
+          <t>174255007</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sitting diastolic blood pressure (observable entity)</t>
+          <t>Non-invasive diastolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4569,12 +4569,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>723232008</t>
+          <t>251070002</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Average blood pressure (observable entity)</t>
+          <t>Non-invasive systolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>723237002</t>
+          <t>251076008</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Non-invasive blood pressure (observable entity)</t>
+          <t>Non-invasive arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4633,12 +4633,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1091811000000102</t>
+          <t>271649006</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Diastolic arterial pressure (observable entity)</t>
+          <t>Systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>67726005</t>
+          <t>271650006</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Diastolic arterial pressure (observable entity)</t>
+          <t>Diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4697,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>140248005</t>
+          <t>314440001</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sitting blood pressure reading (observable entity)</t>
+          <t>Average systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>95281000000109</t>
+          <t>314453003</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sitting systolic blood pressure</t>
+          <t>Average diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4761,12 +4761,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>95291000000106</t>
+          <t>364090009</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sitting diastolic blood pressure</t>
+          <t>Systemic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4793,12 +4793,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>95691000146106</t>
+          <t>386534000</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blood pressure using automatic blood pressure monitor (observable entity)</t>
+          <t>Arterial blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>100151000000109</t>
+          <t>386536003</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sitting systolic blood pressure</t>
+          <t>Systemic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4857,12 +4857,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>100161000000107</t>
+          <t>407554009</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sitting diastolic blood pressure</t>
+          <t>Sitting systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>87179004</t>
+          <t>407555005</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Arterial pulse pressure (observable entity)</t>
+          <t>Sitting diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4921,12 +4921,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1285244000</t>
+          <t>723232008</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mean arterial pressure (observable entity)</t>
+          <t>Average blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2385941000000108</t>
+          <t>723237002</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blood pressure measured in left upper arm (observable entity)</t>
+          <t>Non-invasive blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -4985,12 +4985,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2385951000000106</t>
+          <t>1091811000000102</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blood pressure measured in right upper arm (observable entity)</t>
+          <t>Diastolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5017,12 +5017,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>250765005</t>
+          <t>67726005</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blood pressure (observable entity)</t>
+          <t>Diastolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>251072005</t>
+          <t>140248005</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Non-invasive diastolic arterial pressure (observable entity)</t>
+          <t>Sitting blood pressure reading (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>811751000000106</t>
+          <t>95281000000109</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Arterial pulse pressure (observable entity)</t>
+          <t>Sitting systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -5113,12 +5113,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>832171000000103</t>
+          <t>95291000000106</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Arterial pulse pressure</t>
+          <t>Sitting diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>918041000000108</t>
+          <t>95691000146106</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Average systolic blood pressure</t>
+          <t>Blood pressure using automatic blood pressure monitor (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5177,12 +5177,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>918051000000106</t>
+          <t>100151000000109</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Average diastolic blood pressure</t>
+          <t>Sitting systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -5194,27 +5194,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>314445006</t>
+          <t>100161000000107</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Average night interval systolic blood pressure (observable entity)</t>
+          <t>Sitting diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -5226,27 +5226,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>314446007</t>
+          <t>87179004</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Average day interval systolic blood pressure (observable entity)</t>
+          <t>Arterial pulse pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5258,27 +5258,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>314449000</t>
+          <t>1285244000</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Average 24 hour systolic blood pressure (observable entity)</t>
+          <t>Mean arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5290,27 +5290,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>314460009</t>
+          <t>2385941000000108</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Average night interval diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure measured in left upper arm (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5322,27 +5322,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>314461008</t>
+          <t>2385951000000106</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Average day interval diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure measured in right upper arm (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5354,27 +5354,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>314462001</t>
+          <t>250765005</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Average 24 hour diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5386,27 +5386,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>314463006</t>
+          <t>251072005</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>24 hour blood pressure (observable entity)</t>
+          <t>Non-invasive diastolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5418,27 +5418,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>314464000</t>
+          <t>811751000000106</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>24 hour systolic blood pressure (observable entity)</t>
+          <t>Arterial pulse pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5450,27 +5450,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>314465004</t>
+          <t>832171000000103</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>24 hour diastolic blood pressure (observable entity)</t>
+          <t>Arterial pulse pressure</t>
         </is>
       </c>
     </row>
@@ -5482,27 +5482,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>413605002</t>
+          <t>918041000000108</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Average home diastolic blood pressure (observable entity)</t>
+          <t>Average systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -5514,27 +5514,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>413606001</t>
+          <t>918051000000106</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Average home systolic blood pressure (observable entity)</t>
+          <t>Average diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -5561,12 +5561,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1162735000</t>
+          <t>314445006</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Self reported diastolic blood pressure (observable entity)</t>
+          <t>Average night interval systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5593,12 +5593,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1162737008</t>
+          <t>314446007</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Self reported systolic blood pressure (observable entity)</t>
+          <t>Average day interval systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5625,12 +5625,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>1285115008</t>
+          <t>314449000</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Average home blood pressure (observable entity)</t>
+          <t>Average 24 hour systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5657,12 +5657,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>198081000000101</t>
+          <t>314460009</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ambulatory systolic blood pressure (observable entity)</t>
+          <t>Average night interval diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5689,12 +5689,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>198091000000104</t>
+          <t>314461008</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ambulatory diastolic blood pressure (observable entity)</t>
+          <t>Average day interval diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5721,12 +5721,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>335661000000109</t>
+          <t>314462001</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Self measured blood pressure reading (observable entity)</t>
+          <t>Average 24 hour diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>116711000000107</t>
+          <t>314463006</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blood pressure recorded by patient at home</t>
+          <t>24 hour blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5785,12 +5785,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>121281000000107</t>
+          <t>314464000</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Blood pressure recorded by patient at home</t>
+          <t>24 hour systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5817,12 +5817,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>213031000000105</t>
+          <t>314465004</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ambulatory systolic blood pressure</t>
+          <t>24 hour diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>213041000000101</t>
+          <t>413605002</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ambulatory systolic blood pressure</t>
+          <t>Average home diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>213051000000103</t>
+          <t>413606001</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ambulatory diastolic blood pressure</t>
+          <t>Average home systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5913,12 +5913,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>213061000000100</t>
+          <t>1162735000</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ambulatory diastolic blood pressure</t>
+          <t>Self reported diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5945,12 +5945,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>337061000000109</t>
+          <t>1162737008</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Self measured blood pressure reading</t>
+          <t>Self reported systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -5977,12 +5977,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>337501000000104</t>
+          <t>1285115008</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Self measured blood pressure reading</t>
+          <t>Average home blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6009,12 +6009,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2181371000000107</t>
+          <t>198081000000101</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Average ambulatory blood pressure (observable entity)</t>
+          <t>Ambulatory systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6041,12 +6041,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2181381000000109</t>
+          <t>198091000000104</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Average ambulatory systolic blood pressure (observable entity)</t>
+          <t>Ambulatory diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2181391000000106</t>
+          <t>335661000000109</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Average ambulatory diastolic blood pressure (observable entity)</t>
+          <t>Self measured blood pressure reading (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6105,12 +6105,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2181401000000109</t>
+          <t>116711000000107</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Average ambulatory day interval systolic blood pressure (observable entity)</t>
+          <t>Blood pressure recorded by patient at home</t>
         </is>
       </c>
     </row>
@@ -6137,12 +6137,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2181411000000106</t>
+          <t>121281000000107</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Average ambulatory day interval diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure recorded by patient at home</t>
         </is>
       </c>
     </row>
@@ -6169,12 +6169,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2181421000000100</t>
+          <t>213031000000105</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Average ambulatory night interval systolic blood pressure (observable entity)</t>
+          <t>Ambulatory systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2181431000000103</t>
+          <t>213041000000101</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Average ambulatory night interval diastolic blood pressure (observable entity)</t>
+          <t>Ambulatory systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -6233,12 +6233,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2314241000000104</t>
+          <t>213051000000103</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ambulatory blood pressure (observable entity)</t>
+          <t>Ambulatory diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -6265,12 +6265,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2324511000000105</t>
+          <t>213061000000100</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Average 24 hour blood pressure (observable entity)</t>
+          <t>Ambulatory diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -6297,12 +6297,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2324521000000104</t>
+          <t>337061000000109</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Average day interval blood pressure (observable entity)</t>
+          <t>Self measured blood pressure reading</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2324531000000102</t>
+          <t>337501000000104</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Average night interval blood pressure (observable entity)</t>
+          <t>Self measured blood pressure reading</t>
         </is>
       </c>
     </row>
@@ -6361,12 +6361,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2325001000000103</t>
+          <t>2181371000000107</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Average ambulatory night interval blood pressure (observable entity)</t>
+          <t>Average ambulatory blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6393,12 +6393,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2325011000000101</t>
+          <t>2181381000000109</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Average ambulatory day interval blood pressure (observable entity)</t>
+          <t>Average ambulatory systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>165011000000100</t>
+          <t>2181391000000106</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Average 24 hour diastolic blood pressure</t>
+          <t>Average ambulatory diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>165021000000106</t>
+          <t>2181401000000109</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Average 24 hour systolic blood pressure</t>
+          <t>Average ambulatory day interval systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>165031000000108</t>
+          <t>2181411000000106</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Average day interval diastolic blood pressure</t>
+          <t>Average ambulatory day interval diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>165041000000104</t>
+          <t>2181421000000100</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Average day interval systolic blood pressure</t>
+          <t>Average ambulatory night interval systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>165051000000101</t>
+          <t>2181431000000103</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Average night interval diastolic blood pressure</t>
+          <t>Average ambulatory night interval diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>165061000000103</t>
+          <t>2314241000000104</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Average night interval systolic blood pressure</t>
+          <t>Ambulatory blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6617,12 +6617,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>165071000000105</t>
+          <t>2324511000000105</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Average home diastolic blood pressure</t>
+          <t>Average 24 hour blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>165081000000107</t>
+          <t>2324521000000104</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Average home systolic blood pressure</t>
+          <t>Average day interval blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6681,12 +6681,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>167061000000106</t>
+          <t>2324531000000102</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Average 24 hour diastolic blood pressure</t>
+          <t>Average night interval blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6713,12 +6713,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>167071000000104</t>
+          <t>2325001000000103</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Average 24 hour systolic blood pressure</t>
+          <t>Average ambulatory night interval blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6745,12 +6745,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>167081000000102</t>
+          <t>2325011000000101</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Average day interval diastolic blood pressure</t>
+          <t>Average ambulatory day interval blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -6777,12 +6777,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>167091000000100</t>
+          <t>165011000000100</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Average day interval systolic blood pressure</t>
+          <t>Average 24 hour diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6809,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>167101000000108</t>
+          <t>165021000000106</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Average night interval diastolic blood pressure</t>
+          <t>Average 24 hour systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -6841,12 +6841,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>167111000000105</t>
+          <t>165031000000108</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Average night interval systolic blood pressure</t>
+          <t>Average day interval diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>167121000000104</t>
+          <t>165041000000104</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Average home diastolic blood pressure</t>
+          <t>Average day interval systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>167131000000102</t>
+          <t>165051000000101</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Average home systolic blood pressure</t>
+          <t>Average night interval diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -6937,12 +6937,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>924491000000106</t>
+          <t>165061000000103</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Self-monitoring of blood pressure</t>
+          <t>Average night interval systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -6954,27 +6954,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HOMEBPDEC_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>999028571000230109</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Codes indicating patient chosen not to undertake home blood pressure measurement (HBPM)</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1085031000000100</t>
+          <t>165071000000105</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Home blood pressure monitoring declined (situation)</t>
+          <t>Average home diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -6986,27 +6986,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HTMAX_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>999006651000230109</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Codes for maximal blood pressure (BP) therapy</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>407567007</t>
+          <t>165081000000107</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Patient on maximal tolerated antihypertensive therapy (finding)</t>
+          <t>Average home systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -7018,27 +7018,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>HTMAX_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>999006651000230109</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Codes for maximal blood pressure (BP) therapy</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>104861000000105</t>
+          <t>167061000000106</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Patient on maximal tolerated antihypertensive therapy</t>
+          <t>Average 24 hour diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -7050,27 +7050,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HTMAX_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>999006651000230109</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Codes for maximal blood pressure (BP) therapy</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>107411000000104</t>
+          <t>167071000000104</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Patient on maximal tolerated antihypertensive therapy</t>
+          <t>Average 24 hour systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -7082,27 +7082,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>185719002</t>
+          <t>167081000000102</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Hypertension monitoring first letter (procedure)</t>
+          <t>Average day interval diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -7114,27 +7114,27 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>185720008</t>
+          <t>167091000000100</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Hypertension monitoring second letter (procedure)</t>
+          <t>Average day interval systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -7146,27 +7146,27 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>185721007</t>
+          <t>167101000000108</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Hypertension monitoring third letter (procedure)</t>
+          <t>Average night interval diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -7178,27 +7178,27 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>185722000</t>
+          <t>167111000000105</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Hypertension monitoring verbal invite (procedure)</t>
+          <t>Average night interval systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -7210,27 +7210,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>185723005</t>
+          <t>167121000000104</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hypertension monitoring telephone invite (procedure)</t>
+          <t>Average home diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -7242,27 +7242,27 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>310427004</t>
+          <t>167131000000102</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Hypertension monitoring invitation (procedure)</t>
+          <t>Average home systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -7274,27 +7274,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>143421000000106</t>
+          <t>924491000000106</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Quality and Outcomes Framework hypertension quality indicator-related care invitation using preferred method of communication (procedure)</t>
+          <t>Self-monitoring of blood pressure</t>
         </is>
       </c>
     </row>
@@ -7306,27 +7306,27 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEBPDEC_COD</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999028571000230109</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Codes indicating patient chosen not to undertake home blood pressure measurement (HBPM)</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>1066941000000104</t>
+          <t>1085031000000100</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Hypertension monitoring invitation short message service text message (procedure)</t>
+          <t>Home blood pressure monitoring declined (situation)</t>
         </is>
       </c>
     </row>
@@ -7338,27 +7338,27 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HTMAX_COD</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999006651000230109</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Codes for maximal blood pressure (BP) therapy</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>1066951000000101</t>
+          <t>407567007</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Hypertension monitoring short message service text message first invitation (procedure)</t>
+          <t>Patient on maximal tolerated antihypertensive therapy (finding)</t>
         </is>
       </c>
     </row>
@@ -7370,27 +7370,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HTMAX_COD</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999006651000230109</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Codes for maximal blood pressure (BP) therapy</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>1066961000000103</t>
+          <t>104861000000105</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Hypertension monitoring short message service text message second invitation (procedure)</t>
+          <t>Patient on maximal tolerated antihypertensive therapy</t>
         </is>
       </c>
     </row>
@@ -7402,27 +7402,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HTMAX_COD</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999006651000230109</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Codes for maximal blood pressure (BP) therapy</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>1066971000000105</t>
+          <t>107411000000104</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Hypertension monitoring short message service text message third invitation (procedure)</t>
+          <t>Patient on maximal tolerated antihypertensive therapy</t>
         </is>
       </c>
     </row>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>1083101000000106</t>
+          <t>185719002</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Hypertension monitoring invitation email (procedure)</t>
+          <t>Hypertension monitoring first letter (procedure)</t>
         </is>
       </c>
     </row>
@@ -7481,12 +7481,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>1109921000000106</t>
+          <t>185720008</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Quality and Outcomes Framework quality indicator-related care invitation (procedure)</t>
+          <t>Hypertension monitoring second letter (procedure)</t>
         </is>
       </c>
     </row>
@@ -7513,12 +7513,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>1110941000000107</t>
+          <t>185721007</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Quality and Outcomes Framework hypertension quality indicator-related care invitation (procedure)</t>
+          <t>Hypertension monitoring third letter (procedure)</t>
         </is>
       </c>
     </row>
@@ -7545,12 +7545,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>153898009</t>
+          <t>185722000</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Hypertension monitoring first letter (regime/therapy)</t>
+          <t>Hypertension monitoring verbal invite (procedure)</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>153899001</t>
+          <t>185723005</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Hypertension monitoring second letter (regime/therapy)</t>
+          <t>Hypertension monitoring telephone invite (procedure)</t>
         </is>
       </c>
     </row>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>153900006</t>
+          <t>310427004</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Hypertension monitoring third letter (regime/therapy)</t>
+          <t>Hypertension monitoring invitation (procedure)</t>
         </is>
       </c>
     </row>
@@ -7641,12 +7641,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>153901005</t>
+          <t>143421000000106</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Hypertension monitoring verbal invite (regime/therapy)</t>
+          <t>Quality and Outcomes Framework hypertension quality indicator-related care invitation using preferred method of communication (procedure)</t>
         </is>
       </c>
     </row>
@@ -7673,364 +7673,364 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>153902003</t>
+          <t>1066941000000104</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Hypertension monitoring telephone invite (regime/therapy)</t>
+          <t>Hypertension monitoring invitation short message service text message (procedure)</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HYP009</t>
+          <t>HYP008</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ABPMDEC_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>999028531000230107</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Codes indicating patient has chosen not to undertake ambulatory blood pressure monitoring (ABPM)</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>861231000000105</t>
+          <t>1066951000000101</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ambulatory blood pressure recording declined (situation)</t>
+          <t>Hypertension monitoring short message service text message first invitation (procedure)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>HYP009</t>
+          <t>HYP008</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ABPMDEC_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>999028531000230107</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Codes indicating patient has chosen not to undertake ambulatory blood pressure monitoring (ABPM)</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>861241000000101</t>
+          <t>1066961000000103</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Ambulatory blood pressure recording declined</t>
+          <t>Hypertension monitoring short message service text message second invitation (procedure)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>HYP009</t>
+          <t>HYP008</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>BPDEC_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>999012611000230106</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>413123006</t>
+          <t>1066971000000105</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Blood pressure procedure declined (situation)</t>
+          <t>Hypertension monitoring short message service text message third invitation (procedure)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>HYP009</t>
+          <t>HYP008</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>BPDEC_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>999012611000230106</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>117221000000107</t>
+          <t>1083101000000106</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Blood pressure procedure refused</t>
+          <t>Hypertension monitoring invitation email (procedure)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>HYP009</t>
+          <t>HYP008</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>BPDEC_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>999012611000230106</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>121961000000108</t>
+          <t>1109921000000106</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Blood pressure procedure refused</t>
+          <t>Quality and Outcomes Framework quality indicator-related care invitation (procedure)</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HYP009</t>
+          <t>HYP008</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>6797001</t>
+          <t>1110941000000107</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Mean blood pressure (observable entity)</t>
+          <t>Quality and Outcomes Framework hypertension quality indicator-related care invitation (procedure)</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HYP009</t>
+          <t>HYP008</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>72313002</t>
+          <t>153898009</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Systolic arterial pressure (observable entity)</t>
+          <t>Hypertension monitoring first letter (regime/therapy)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HYP009</t>
+          <t>HYP008</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>75367002</t>
+          <t>153899001</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Blood pressure (observable entity)</t>
+          <t>Hypertension monitoring second letter (regime/therapy)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HYP009</t>
+          <t>HYP008</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>163035008</t>
+          <t>153900006</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sitting blood pressure (observable entity)</t>
+          <t>Hypertension monitoring third letter (regime/therapy)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HYP009</t>
+          <t>HYP008</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>174255007</t>
+          <t>153901005</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Non-invasive diastolic arterial pressure (observable entity)</t>
+          <t>Hypertension monitoring verbal invite (regime/therapy)</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HYP009</t>
+          <t>HYP008</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>251070002</t>
+          <t>153902003</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Non-invasive systolic arterial pressure (observable entity)</t>
+          <t>Hypertension monitoring telephone invite (regime/therapy)</t>
         </is>
       </c>
     </row>
@@ -8042,27 +8042,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>ABPMDEC_COD</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999028531000230107</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Codes indicating patient has chosen not to undertake ambulatory blood pressure monitoring (ABPM)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>251076008</t>
+          <t>861231000000105</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Non-invasive arterial pressure (observable entity)</t>
+          <t>Ambulatory blood pressure recording declined (situation)</t>
         </is>
       </c>
     </row>
@@ -8074,27 +8074,27 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>ABPMDEC_COD</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999028531000230107</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Codes indicating patient has chosen not to undertake ambulatory blood pressure monitoring (ABPM)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>271649006</t>
+          <t>861241000000101</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Systolic blood pressure (observable entity)</t>
+          <t>Ambulatory blood pressure recording declined</t>
         </is>
       </c>
     </row>
@@ -8106,27 +8106,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>BPDEC_COD</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012611000230106</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>271650006</t>
+          <t>413123006</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure procedure declined (situation)</t>
         </is>
       </c>
     </row>
@@ -8138,27 +8138,27 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>BPDEC_COD</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012611000230106</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>314440001</t>
+          <t>117221000000107</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Average systolic blood pressure (observable entity)</t>
+          <t>Blood pressure procedure refused</t>
         </is>
       </c>
     </row>
@@ -8170,27 +8170,27 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>CLINBP_COD</t>
+          <t>BPDEC_COD</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>999036281000230108</t>
+          <t>999012611000230106</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
+          <t>Codes indicating the patient has chosen not to have blood pressure procedure</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>314453003</t>
+          <t>121961000000108</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Average diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure procedure refused</t>
         </is>
       </c>
     </row>
@@ -8217,12 +8217,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>364090009</t>
+          <t>6797001</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Systemic arterial pressure (observable entity)</t>
+          <t>Mean blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>386534000</t>
+          <t>72313002</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Arterial blood pressure (observable entity)</t>
+          <t>Systolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8281,12 +8281,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>386536003</t>
+          <t>75367002</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Systemic blood pressure (observable entity)</t>
+          <t>Blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8313,12 +8313,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>407554009</t>
+          <t>163035008</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Sitting systolic blood pressure (observable entity)</t>
+          <t>Sitting blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>407555005</t>
+          <t>174255007</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Sitting diastolic blood pressure (observable entity)</t>
+          <t>Non-invasive diastolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>723232008</t>
+          <t>251070002</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Average blood pressure (observable entity)</t>
+          <t>Non-invasive systolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8409,12 +8409,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>723237002</t>
+          <t>251076008</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Non-invasive blood pressure (observable entity)</t>
+          <t>Non-invasive arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8441,12 +8441,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>1091811000000102</t>
+          <t>271649006</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Diastolic arterial pressure (observable entity)</t>
+          <t>Systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8473,12 +8473,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>67726005</t>
+          <t>271650006</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Diastolic arterial pressure (observable entity)</t>
+          <t>Diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8505,12 +8505,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>140248005</t>
+          <t>314440001</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Sitting blood pressure reading (observable entity)</t>
+          <t>Average systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8537,12 +8537,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>95281000000109</t>
+          <t>314453003</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Sitting systolic blood pressure</t>
+          <t>Average diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8569,12 +8569,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>95291000000106</t>
+          <t>364090009</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Sitting diastolic blood pressure</t>
+          <t>Systemic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8601,12 +8601,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>95691000146106</t>
+          <t>386534000</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Blood pressure using automatic blood pressure monitor (observable entity)</t>
+          <t>Arterial blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8633,12 +8633,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>100151000000109</t>
+          <t>386536003</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Sitting systolic blood pressure</t>
+          <t>Systemic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8665,12 +8665,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>100161000000107</t>
+          <t>407554009</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sitting diastolic blood pressure</t>
+          <t>Sitting systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>87179004</t>
+          <t>407555005</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Arterial pulse pressure (observable entity)</t>
+          <t>Sitting diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>1285244000</t>
+          <t>723232008</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mean arterial pressure (observable entity)</t>
+          <t>Average blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8761,12 +8761,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2385941000000108</t>
+          <t>723237002</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Blood pressure measured in left upper arm (observable entity)</t>
+          <t>Non-invasive blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8793,12 +8793,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2385951000000106</t>
+          <t>1091811000000102</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Blood pressure measured in right upper arm (observable entity)</t>
+          <t>Diastolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8825,12 +8825,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>250765005</t>
+          <t>67726005</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Blood pressure (observable entity)</t>
+          <t>Diastolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8857,12 +8857,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>251072005</t>
+          <t>140248005</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Non-invasive diastolic arterial pressure (observable entity)</t>
+          <t>Sitting blood pressure reading (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8889,12 +8889,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>811751000000106</t>
+          <t>95281000000109</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Arterial pulse pressure (observable entity)</t>
+          <t>Sitting systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>832171000000103</t>
+          <t>95291000000106</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Arterial pulse pressure</t>
+          <t>Sitting diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>918041000000108</t>
+          <t>95691000146106</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Average systolic blood pressure</t>
+          <t>Blood pressure using automatic blood pressure monitor (observable entity)</t>
         </is>
       </c>
     </row>
@@ -8985,12 +8985,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>918051000000106</t>
+          <t>100151000000109</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Average diastolic blood pressure</t>
+          <t>Sitting systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -9002,27 +9002,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>314445006</t>
+          <t>100161000000107</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Average night interval systolic blood pressure (observable entity)</t>
+          <t>Sitting diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -9034,27 +9034,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>314446007</t>
+          <t>87179004</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Average day interval systolic blood pressure (observable entity)</t>
+          <t>Arterial pulse pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9066,27 +9066,27 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>314449000</t>
+          <t>1285244000</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Average 24 hour systolic blood pressure (observable entity)</t>
+          <t>Mean arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9098,27 +9098,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>314460009</t>
+          <t>2385941000000108</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Average night interval diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure measured in left upper arm (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9130,27 +9130,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>314461008</t>
+          <t>2385951000000106</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Average day interval diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure measured in right upper arm (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9162,27 +9162,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>314462001</t>
+          <t>250765005</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Average 24 hour diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9194,27 +9194,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>314463006</t>
+          <t>251072005</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>24 hour blood pressure (observable entity)</t>
+          <t>Non-invasive diastolic arterial pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9226,27 +9226,27 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>314464000</t>
+          <t>811751000000106</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>24 hour systolic blood pressure (observable entity)</t>
+          <t>Arterial pulse pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9258,27 +9258,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>314465004</t>
+          <t>832171000000103</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>24 hour diastolic blood pressure (observable entity)</t>
+          <t>Arterial pulse pressure</t>
         </is>
       </c>
     </row>
@@ -9290,27 +9290,27 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>413605002</t>
+          <t>918041000000108</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Average home diastolic blood pressure (observable entity)</t>
+          <t>Average systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -9322,27 +9322,27 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>HOMEAMBBP_COD</t>
+          <t>CLINBP_COD</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>999036291000230105</t>
+          <t>999036281000230108</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Home and ambulatory blood pressure recording codes</t>
+          <t>Blood pressure recording codes excluding home and ambulatory blood pressure</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>413606001</t>
+          <t>918051000000106</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Average home systolic blood pressure (observable entity)</t>
+          <t>Average diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -9369,12 +9369,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>1162735000</t>
+          <t>314445006</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Self reported diastolic blood pressure (observable entity)</t>
+          <t>Average night interval systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9401,12 +9401,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>1162737008</t>
+          <t>314446007</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Self reported systolic blood pressure (observable entity)</t>
+          <t>Average day interval systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9433,12 +9433,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>1285115008</t>
+          <t>314449000</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Average home blood pressure (observable entity)</t>
+          <t>Average 24 hour systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9465,12 +9465,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>198081000000101</t>
+          <t>314460009</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Ambulatory systolic blood pressure (observable entity)</t>
+          <t>Average night interval diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9497,12 +9497,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>198091000000104</t>
+          <t>314461008</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Ambulatory diastolic blood pressure (observable entity)</t>
+          <t>Average day interval diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9529,12 +9529,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>335661000000109</t>
+          <t>314462001</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Self measured blood pressure reading (observable entity)</t>
+          <t>Average 24 hour diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9561,12 +9561,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>116711000000107</t>
+          <t>314463006</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Blood pressure recorded by patient at home</t>
+          <t>24 hour blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9593,12 +9593,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>121281000000107</t>
+          <t>314464000</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Blood pressure recorded by patient at home</t>
+          <t>24 hour systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9625,12 +9625,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>213031000000105</t>
+          <t>314465004</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Ambulatory systolic blood pressure</t>
+          <t>24 hour diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>213041000000101</t>
+          <t>413605002</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Ambulatory systolic blood pressure</t>
+          <t>Average home diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9689,12 +9689,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>213051000000103</t>
+          <t>413606001</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Ambulatory diastolic blood pressure</t>
+          <t>Average home systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9721,12 +9721,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>213061000000100</t>
+          <t>1162735000</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Ambulatory diastolic blood pressure</t>
+          <t>Self reported diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9753,12 +9753,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>337061000000109</t>
+          <t>1162737008</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Self measured blood pressure reading</t>
+          <t>Self reported systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9785,12 +9785,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>337501000000104</t>
+          <t>1285115008</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Self measured blood pressure reading</t>
+          <t>Average home blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9817,12 +9817,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2181371000000107</t>
+          <t>198081000000101</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Average ambulatory blood pressure (observable entity)</t>
+          <t>Ambulatory systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9849,12 +9849,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2181381000000109</t>
+          <t>198091000000104</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Average ambulatory systolic blood pressure (observable entity)</t>
+          <t>Ambulatory diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9881,12 +9881,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2181391000000106</t>
+          <t>335661000000109</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Average ambulatory diastolic blood pressure (observable entity)</t>
+          <t>Self measured blood pressure reading (observable entity)</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9913,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2181401000000109</t>
+          <t>116711000000107</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Average ambulatory day interval systolic blood pressure (observable entity)</t>
+          <t>Blood pressure recorded by patient at home</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2181411000000106</t>
+          <t>121281000000107</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Average ambulatory day interval diastolic blood pressure (observable entity)</t>
+          <t>Blood pressure recorded by patient at home</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2181421000000100</t>
+          <t>213031000000105</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Average ambulatory night interval systolic blood pressure (observable entity)</t>
+          <t>Ambulatory systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10009,12 +10009,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2181431000000103</t>
+          <t>213041000000101</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Average ambulatory night interval diastolic blood pressure (observable entity)</t>
+          <t>Ambulatory systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10041,12 +10041,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2314241000000104</t>
+          <t>213051000000103</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Ambulatory blood pressure (observable entity)</t>
+          <t>Ambulatory diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10073,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2324511000000105</t>
+          <t>213061000000100</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Average 24 hour blood pressure (observable entity)</t>
+          <t>Ambulatory diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10105,12 +10105,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2324521000000104</t>
+          <t>337061000000109</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Average day interval blood pressure (observable entity)</t>
+          <t>Self measured blood pressure reading</t>
         </is>
       </c>
     </row>
@@ -10137,12 +10137,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2324531000000102</t>
+          <t>337501000000104</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Average night interval blood pressure (observable entity)</t>
+          <t>Self measured blood pressure reading</t>
         </is>
       </c>
     </row>
@@ -10169,12 +10169,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2325001000000103</t>
+          <t>2181371000000107</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Average ambulatory night interval blood pressure (observable entity)</t>
+          <t>Average ambulatory blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10201,12 +10201,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2325011000000101</t>
+          <t>2181381000000109</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Average ambulatory day interval blood pressure (observable entity)</t>
+          <t>Average ambulatory systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>165011000000100</t>
+          <t>2181391000000106</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Average 24 hour diastolic blood pressure</t>
+          <t>Average ambulatory diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10265,12 +10265,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>165021000000106</t>
+          <t>2181401000000109</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Average 24 hour systolic blood pressure</t>
+          <t>Average ambulatory day interval systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10297,12 +10297,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>165031000000108</t>
+          <t>2181411000000106</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Average day interval diastolic blood pressure</t>
+          <t>Average ambulatory day interval diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10329,12 +10329,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>165041000000104</t>
+          <t>2181421000000100</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Average day interval systolic blood pressure</t>
+          <t>Average ambulatory night interval systolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10361,12 +10361,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>165051000000101</t>
+          <t>2181431000000103</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Average night interval diastolic blood pressure</t>
+          <t>Average ambulatory night interval diastolic blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10393,12 +10393,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>165061000000103</t>
+          <t>2314241000000104</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Average night interval systolic blood pressure</t>
+          <t>Ambulatory blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10425,12 +10425,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>165071000000105</t>
+          <t>2324511000000105</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Average home diastolic blood pressure</t>
+          <t>Average 24 hour blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10457,12 +10457,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>165081000000107</t>
+          <t>2324521000000104</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Average home systolic blood pressure</t>
+          <t>Average day interval blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10489,12 +10489,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>167061000000106</t>
+          <t>2324531000000102</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Average 24 hour diastolic blood pressure</t>
+          <t>Average night interval blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10521,12 +10521,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>167071000000104</t>
+          <t>2325001000000103</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Average 24 hour systolic blood pressure</t>
+          <t>Average ambulatory night interval blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10553,12 +10553,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>167081000000102</t>
+          <t>2325011000000101</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Average day interval diastolic blood pressure</t>
+          <t>Average ambulatory day interval blood pressure (observable entity)</t>
         </is>
       </c>
     </row>
@@ -10585,12 +10585,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>167091000000100</t>
+          <t>165011000000100</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Average day interval systolic blood pressure</t>
+          <t>Average 24 hour diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>167101000000108</t>
+          <t>165021000000106</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Average night interval diastolic blood pressure</t>
+          <t>Average 24 hour systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>167111000000105</t>
+          <t>165031000000108</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Average night interval systolic blood pressure</t>
+          <t>Average day interval diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10681,12 +10681,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>167121000000104</t>
+          <t>165041000000104</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Average home diastolic blood pressure</t>
+          <t>Average day interval systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10713,12 +10713,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>167131000000102</t>
+          <t>165051000000101</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Average home systolic blood pressure</t>
+          <t>Average night interval diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>924491000000106</t>
+          <t>165061000000103</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Self-monitoring of blood pressure</t>
+          <t>Average night interval systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10762,27 +10762,27 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>HOMEBPDEC_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>999028571000230109</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Codes indicating patient chosen not to undertake home blood pressure measurement (HBPM)</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>1085031000000100</t>
+          <t>165071000000105</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Home blood pressure monitoring declined (situation)</t>
+          <t>Average home diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10794,27 +10794,27 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>HTMAX_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>999006651000230109</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Codes for maximal blood pressure (BP) therapy</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>407567007</t>
+          <t>165081000000107</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Patient on maximal tolerated antihypertensive therapy (finding)</t>
+          <t>Average home systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10826,27 +10826,27 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>HTMAX_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>999006651000230109</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Codes for maximal blood pressure (BP) therapy</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>104861000000105</t>
+          <t>167061000000106</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Patient on maximal tolerated antihypertensive therapy</t>
+          <t>Average 24 hour diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10858,27 +10858,27 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>HTMAX_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>999006651000230109</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Codes for maximal blood pressure (BP) therapy</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>107411000000104</t>
+          <t>167071000000104</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Patient on maximal tolerated antihypertensive therapy</t>
+          <t>Average 24 hour systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10890,27 +10890,27 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>185719002</t>
+          <t>167081000000102</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Hypertension monitoring first letter (procedure)</t>
+          <t>Average day interval diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10922,27 +10922,27 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>185720008</t>
+          <t>167091000000100</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Hypertension monitoring second letter (procedure)</t>
+          <t>Average day interval systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10954,27 +10954,27 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>185721007</t>
+          <t>167101000000108</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Hypertension monitoring third letter (procedure)</t>
+          <t>Average night interval diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -10986,27 +10986,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>185722000</t>
+          <t>167111000000105</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Hypertension monitoring verbal invite (procedure)</t>
+          <t>Average night interval systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -11018,27 +11018,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>185723005</t>
+          <t>167121000000104</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Hypertension monitoring telephone invite (procedure)</t>
+          <t>Average home diastolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -11050,27 +11050,27 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>310427004</t>
+          <t>167131000000102</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Hypertension monitoring invitation (procedure)</t>
+          <t>Average home systolic blood pressure</t>
         </is>
       </c>
     </row>
@@ -11082,27 +11082,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEAMBBP_COD</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999036291000230105</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Home and ambulatory blood pressure recording codes</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>143421000000106</t>
+          <t>924491000000106</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Quality and Outcomes Framework hypertension quality indicator-related care invitation using preferred method of communication (procedure)</t>
+          <t>Self-monitoring of blood pressure</t>
         </is>
       </c>
     </row>
@@ -11114,27 +11114,27 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HOMEBPDEC_COD</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999028571000230109</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Codes indicating patient chosen not to undertake home blood pressure measurement (HBPM)</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>1066941000000104</t>
+          <t>1085031000000100</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Hypertension monitoring invitation short message service text message (procedure)</t>
+          <t>Home blood pressure monitoring declined (situation)</t>
         </is>
       </c>
     </row>
@@ -11146,27 +11146,27 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HTMAX_COD</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999006651000230109</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Codes for maximal blood pressure (BP) therapy</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>1066951000000101</t>
+          <t>407567007</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Hypertension monitoring short message service text message first invitation (procedure)</t>
+          <t>Patient on maximal tolerated antihypertensive therapy (finding)</t>
         </is>
       </c>
     </row>
@@ -11178,27 +11178,27 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HTMAX_COD</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999006651000230109</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Codes for maximal blood pressure (BP) therapy</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>1066961000000103</t>
+          <t>104861000000105</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Hypertension monitoring short message service text message second invitation (procedure)</t>
+          <t>Patient on maximal tolerated antihypertensive therapy</t>
         </is>
       </c>
     </row>
@@ -11210,27 +11210,27 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>HYPINVITE_COD</t>
+          <t>HTMAX_COD</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>999012971000230108</t>
+          <t>999006651000230109</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Invite for hypertension care review codes</t>
+          <t>Codes for maximal blood pressure (BP) therapy</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>1066971000000105</t>
+          <t>107411000000104</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Hypertension monitoring short message service text message third invitation (procedure)</t>
+          <t>Patient on maximal tolerated antihypertensive therapy</t>
         </is>
       </c>
     </row>
@@ -11257,12 +11257,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>1083101000000106</t>
+          <t>185719002</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Hypertension monitoring invitation email (procedure)</t>
+          <t>Hypertension monitoring first letter (procedure)</t>
         </is>
       </c>
     </row>
@@ -11289,12 +11289,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>1109921000000106</t>
+          <t>185720008</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Quality and Outcomes Framework quality indicator-related care invitation (procedure)</t>
+          <t>Hypertension monitoring second letter (procedure)</t>
         </is>
       </c>
     </row>
@@ -11321,12 +11321,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>1110941000000107</t>
+          <t>185721007</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Quality and Outcomes Framework hypertension quality indicator-related care invitation (procedure)</t>
+          <t>Hypertension monitoring third letter (procedure)</t>
         </is>
       </c>
     </row>
@@ -11353,12 +11353,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>153898009</t>
+          <t>185722000</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Hypertension monitoring first letter (regime/therapy)</t>
+          <t>Hypertension monitoring verbal invite (procedure)</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>153899001</t>
+          <t>185723005</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Hypertension monitoring second letter (regime/therapy)</t>
+          <t>Hypertension monitoring telephone invite (procedure)</t>
         </is>
       </c>
     </row>
@@ -11417,12 +11417,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>153900006</t>
+          <t>310427004</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Hypertension monitoring third letter (regime/therapy)</t>
+          <t>Hypertension monitoring invitation (procedure)</t>
         </is>
       </c>
     </row>
@@ -11449,12 +11449,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>153901005</t>
+          <t>143421000000106</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Hypertension monitoring verbal invite (regime/therapy)</t>
+          <t>Quality and Outcomes Framework hypertension quality indicator-related care invitation using preferred method of communication (procedure)</t>
         </is>
       </c>
     </row>
@@ -11481,76 +11481,76 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>153902003</t>
+          <t>1066941000000104</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Hypertension monitoring telephone invite (regime/therapy)</t>
+          <t>Hypertension monitoring invitation short message service text message (procedure)</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP009</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>HYPPCADEC_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>999013091000230102</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Codes indicating the patient has chosen not to receive hypertension quality indicator care</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>716771000000106</t>
+          <t>1066951000000101</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Excepted from hypertension quality indicators - informed dissent (finding)</t>
+          <t>Hypertension monitoring short message service text message first invitation (procedure)</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>HYP008</t>
+          <t>HYP009</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>HYPPCAPU_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>999013211000230104</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Codes for hypertension quality indicator care unsuitable for patient</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>716821000000100</t>
+          <t>1066961000000103</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Excepted from hypertension quality indicators - patient unsuitable (finding)</t>
+          <t>Hypertension monitoring short message service text message second invitation (procedure)</t>
         </is>
       </c>
     </row>
@@ -11562,27 +11562,27 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>HYPPCADEC_COD</t>
+          <t>HYPINVITE_COD</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>999013091000230102</t>
+          <t>999012971000230108</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Codes indicating the patient has chosen not to receive hypertension quality indicator care</t>
+          <t>Invite for hypertension care review codes</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>716771000000106</t>
+          <t>1066971000000105</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Excepted from hypertension quality indicators - informed dissent (finding)</t>
+          <t>Hypertension monitoring short message service text message third invitation (procedure)</t>
         </is>
       </c>
     </row>
@@ -11594,25 +11594,377 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
+          <t>HYPINVITE_COD</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>999012971000230108</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Invite for hypertension care review codes</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>1083101000000106</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Hypertension monitoring invitation email (procedure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>HYP009</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>HYPINVITE_COD</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>999012971000230108</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Invite for hypertension care review codes</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>1109921000000106</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Quality and Outcomes Framework quality indicator-related care invitation (procedure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>HYP009</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>HYPINVITE_COD</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>999012971000230108</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Invite for hypertension care review codes</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>1110941000000107</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Quality and Outcomes Framework hypertension quality indicator-related care invitation (procedure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>HYP009</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>HYPINVITE_COD</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>999012971000230108</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Invite for hypertension care review codes</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>153898009</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Hypertension monitoring first letter (regime/therapy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>HYP009</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>HYPINVITE_COD</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>999012971000230108</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Invite for hypertension care review codes</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>153899001</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Hypertension monitoring second letter (regime/therapy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>HYP009</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>HYPINVITE_COD</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>999012971000230108</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Invite for hypertension care review codes</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>153900006</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Hypertension monitoring third letter (regime/therapy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>HYP009</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>HYPINVITE_COD</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>999012971000230108</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Invite for hypertension care review codes</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>153901005</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Hypertension monitoring verbal invite (regime/therapy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>HYP009</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>HYPINVITE_COD</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>999012971000230108</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Invite for hypertension care review codes</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>153902003</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Hypertension monitoring telephone invite (regime/therapy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>HYP008</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>HYPPCADEC_COD</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>999013091000230102</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Codes indicating the patient has chosen not to receive hypertension quality indicator care</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>716771000000106</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Excepted from hypertension quality indicators - informed dissent (finding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>HYP008</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
           <t>HYPPCAPU_COD</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C361" t="inlineStr">
         <is>
           <t>999013211000230104</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
+      <c r="D361" t="inlineStr">
         <is>
           <t>Codes for hypertension quality indicator care unsuitable for patient</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr">
+      <c r="E361" t="inlineStr">
         <is>
           <t>716821000000100</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr">
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Excepted from hypertension quality indicators - patient unsuitable (finding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>HYP009</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>HYPPCADEC_COD</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>999013091000230102</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Codes indicating the patient has chosen not to receive hypertension quality indicator care</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>716771000000106</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Excepted from hypertension quality indicators - informed dissent (finding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>HYP009</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>HYPPCAPU_COD</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>999013211000230104</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Codes for hypertension quality indicator care unsuitable for patient</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>716821000000100</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
         <is>
           <t>Excepted from hypertension quality indicators - patient unsuitable (finding)</t>
         </is>
